--- a/Dataset/EN/xlsx/ITAMed_2021_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2021_EN.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>An elderly man is admitted to the pulmonology department for the treatment of pneumonia with intravenous piperacillin/tazobactam. After a few days, he develops diarrhea not associated with fever or abdominal pain. Given the suspicion of Clostridium difficile diarrhea, which of the following interventions is the priority?</t>
+          <t>An elderly patient is admitted to the pulmonology department for the treatment of pneumonia with intravenous piperacillin/tazobactam. After a few days, he develops diarrhea not associated with fever or abdominal pain. Given the suspicion of Clostridium difficile diarrhea, which of the following interventions is the priority?</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>In the case of ventricular fibrillation, electrical defibrillation must be performed:</t>
+          <t>In the case of ventricular fibrillation, electrical defibrillation must be performed</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CT evaluation of a patient reveals a dissection of the ascending aorta, without involvement of the aortic arch. According to the DeBakey classification, this type of dissection is defined as:</t>
+          <t>CT evaluation of a patient reveals a dissection of the ascending aorta, without involvement of the aortic arch. According to the DeBakey classification, this type of dissection is defined as</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A 78-year-old man, bedridden for two weeks following hemiarthroplasty for a femoral neck fracture, presents with a skin lesion in the sacral region, oval-shaped, with irregular margins, red-violaceous in color, which does not blanch on digital pressure, without signs of tissue loss. This is:</t>
+          <t>A 78-year-old man, bedridden for two weeks following hemiarthroplasty for a femoral neck fracture, presents with a skin lesion in the sacral region, oval-shaped, with irregular margins, red-violaceous in color, which does not blanch on digital pressure, without signs of tissue loss. This is</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The treatment of a proximal femur fracture in very advanced age:</t>
+          <t>The treatment of a proximal femur fracture in very advanced age</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Adjuvant chemotherapy is defined as:</t>
+          <t>Adjuvant chemotherapy is defined as</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>An 82-year-old man presents to the "dermatologic emergency" clinic because of the appearance, over the past approximately 2 weeks, of tense blisters on erythematous-edematous skin at the proximal portions of both lower limbs and on the trunk, accompanied by itching and burning, in the absence of obvious triggering factors such as trauma, burns, or drug intake. The most likely diagnosis is:</t>
+          <t>An 82-year-old man presents to the "dermatologic emergency" clinic because of the appearance, over the past approximately 2 weeks, of tense blisters on erythematous-edematous skin at the proximal portions of both lower limbs and on the trunk, accompanied by itching and burning, in the absence of obvious triggering factors such as trauma, burns, or drug intake. The most likely diagnosis is</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>For moderate fatigue, a 44-year-old man undergoes blood tests that document the following complete blood count values: Leukocytes 11,400/mm3 (including neutrophils 8,900/mm3), hemoglobin 11.7 g/dL, MCV 87 fL; platelets 690,000/mm3. The values are confirmed in two subsequent tests. Which of the following tests should be performed:</t>
+          <t>For moderate fatigue, a 44-year-old man undergoes blood tests that document the following complete blood count values: Leukocytes 11,400/mm3 (including neutrophils 8,900/mm3), hemoglobin 11.7 g/dL, MCV 87 fL; platelets 690,000/mm3. The values are confirmed in two subsequent tests. Which of the following tests should be performed</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>All-trans retinoic acid and arsenic trioxide are used for the treatment of:</t>
+          <t>All-trans retinoic acid and arsenic trioxide are used for the treatment of</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a common side effect of thiazide diuretics:</t>
+          <t>Which of the following is NOT a common side effect of thiazide diuretics</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Which of these is NOT a common side effect of ACE inhibitors:</t>
+          <t>Which of these is NOT a common side effect of ACE inhibitors</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A diagnostic thoracentesis is performed on a unilateral pleural effusion. Laboratory analysis of the pleural fluid identifies an exudate, with &gt; 80% lymphocytes among all cells, a normal NT-proBNP concentration, and an absence of eosinophils. Among the following, which is the most likely cause of this pleural effusion:</t>
+          <t>A diagnostic thoracentesis is performed on a unilateral pleural effusion. Laboratory analysis of the pleural fluid identifies an exudate, with &gt; 80% lymphocytes among all cells, a normal NT-proBNP concentration, and an absence of eosinophils. Among the following, which is the most likely cause of this pleural effusion</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A 74-year-old man is diagnosed with community-acquired pneumonia. Based on the CURB-65 prognostic score, the Emergency Department physician decides, after starting appropriate empirical antibiotic therapy, to discharge him and treat him at home. The English acronym CURB-65 stands for:</t>
+          <t>A 74-year-old man is diagnosed with community-acquired pneumonia. Based on the CURB-65 prognostic score, the Emergency Department physician decides, after starting appropriate empirical antibiotic therapy, to discharge him and treat him at home. The English acronym CURB-65 stands for</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>It is decided to administer pre-exposure prophylaxis (PrEP) to an "at-risk" patient to prevent HIV infection. Which of the following drugs (or combination of drugs) is recommended?</t>
+          <t>It is decided to administer pre-exposure prophylaxis (PrEP) to an "at-risk" patient to prevent HIV infection. Which of the following drugs (or drug combinations) is recommended?</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Classic congenital adrenal hyperplasia due to 21-hydroxylase deficiency is characterized by the accumulation of which of the following hormones:</t>
+          <t>Classic congenital adrenal hyperplasia due to 21-hydroxylase deficiency is characterized by the accumulation of which of the following hormones</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Which of the following clinical findings is NOT a criterion for establishing the diagnosis of hemophagocytic lymphohistiocytosis:</t>
+          <t>Which of the following clinical findings is NOT a criterion for establishing the diagnosis of hemophagocytic lymphohistiocytosis</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>The serogroup of Neisseria meningitidis most frequently responsible for invasive meningococcal disease in the first year of life in Italy in recent years (according to the 2019 epidemiological report on invasive bacterial diseases by the Istituto Superiore di Sanità) is:</t>
+          <t>The serogroup of Neisseria meningitidis most frequently responsible for invasive meningococcal disease in the first year of life in Italy in recent years (according to the 2019 epidemiological report on invasive bacterial diseases by the Istituto Superiore di Sanità) is</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Which of the following statements regarding acute epiglottitis in children is incorrect:</t>
+          <t>Which of the following statements regarding acute epiglottitis in children is incorrect</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Which of the following statements about right-sided colon cancer is correct:</t>
+          <t>Which of the following statements about right-sided colon cancer is correct</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Paradoxical dysphagia in the early phase is:</t>
+          <t>Paradoxical dysphagia in the early phase is</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>The most likely cause of abnormal uterine bleeding in adolescence is:</t>
+          <t>The most likely cause of abnormal uterine bleeding in adolescence is</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>The most typical and frequent symptomatology of pelvic endometriosis consists of:</t>
+          <t>The most typical and frequent symptomatology of pelvic endometriosis consists of</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>A 27-year-old woman, with a history of recurrent miscarriage and a prior appendectomy in adolescence, presents to the Emergency Department with a body temperature of 38.3°C, pelvic pain, leukocytosis (WBC 18,000/mm3), and a negative pregnancy test. The most likely diagnostic hypothesis is:</t>
+          <t>A 27-year-old woman, with a history of recurrent miscarriage and a prior appendectomy in adolescence, presents to the Emergency Department with a body temperature of 38.3°C, pelvic pain, leukocytosis (WBC 18,000/mm3), and a negative pregnancy test. The most likely diagnostic hypothesis is</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>A 27-year-old woman undergoes a screening Pap test and receives a result of HSIL (High-Grade Squamous Intraepithelial Lesion) according to the Bethesda System. The correct workup to perform in order to demonstrate the possible presence of a neoplastic lesion of the uterine cervix is:</t>
+          <t>A 27-year-old woman undergoes a screening Pap test and receives a result of HSIL (High-Grade Squamous Intraepithelial Lesion) according to the Bethesda System. The correct workup to perform in order to demonstrate the possible presence of a neoplastic lesion of the uterine cervix is</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>A 13-year-old boy comes to medical attention complaining of right knee pain for several weeks. On physical examination there is swelling and tenderness over the anterior tibial tuberosity at the insertion of the patellar tendon. The boy's clinical presentation and history point toward a diagnosis of:</t>
+          <t>A 13-year-old boy comes to medical attention complaining of right knee pain for several weeks. On physical examination there is swelling and tenderness over the anterior tibial tuberosity at the insertion of the patellar tendon. The boy's clinical presentation and history point toward a diagnosis of</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>A 64-year-old woman reports pain and reduced range of motion of the first metatarsophalangeal joint. On inspection, no local abnormalities are evident, whereas radiographic examination shows signs of osteoarthritis of the first metatarsophalangeal joint. The angle between the 1st and 2nd metatarsals measures 7 degrees and the hallux valgus angle measures 12 degrees. This clinical picture is consistent with:</t>
+          <t>A 64-year-old woman reports pain and reduced range of motion of the first metatarsophalangeal joint. On inspection, no local abnormalities are evident, whereas radiographic examination shows signs of osteoarthritis of the first metatarsophalangeal joint. The angle between the 1st and 2nd metatarsals measures 7 degrees and the hallux valgus angle measures 12 degrees. This clinical picture is consistent with</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>A 36-year-old woman with multiple sclerosis reports the recent onset of urinary urgency and urge urinary incontinence. Which of the following drug classes could be useful for the treatment of this problem:</t>
+          <t>A 36-year-old woman with multiple sclerosis reports the recent onset of urinary urgency and urge urinary incontinence. Which of the following drug classes could be useful for the treatment of this problem</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>A 75-year-old man, with heart disease and hypertension, complains of sudden vision loss in the right eye. With reference to the clinical picture and the fundus photograph above, the most likely diagnosis is:</t>
+          <t>A 75-year-old man, with heart disease and hypertension, complains of sudden vision loss in the right eye. With reference to the clinical picture and the fundus photograph above, the most likely diagnosis is</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>A 37-year-old man goes to the ophthalmologist because he has noticed a reduction in visual acuity when driving at night and especially when reading the newspaper, which he necessarily has to hold farther away. He reports being worried because, until a few years earlier, it had always been his pride to be able to see at a distance much better than his friends. It is most likely that the man:</t>
+          <t>A 37-year-old man goes to the ophthalmologist because he has noticed a reduction in visual acuity when driving at night and especially when reading the newspaper, which he necessarily has to hold farther away. He reports being worried because, until a few years earlier, it had always been his pride to be able to see at a distance much better than his friends. It is most likely that the man</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>A 59-year-old man in good general health presents with a squamous cell carcinoma of the left gingivo-buccal sulcus, cT4aN2cM0. Contrast-enhanced MRI reveals massive infiltration of the mandible. An appropriate therapeutic proposal includes:</t>
+          <t>A 59-year-old man in good general health presents with a squamous cell carcinoma of the left gingivo-buccal sulcus, cT4aN2cM0. Contrast-enhanced MRI reveals massive infiltration of the mandible. An appropriate therapeutic proposal includes</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Pleomorphic adenoma:</t>
+          <t>Pleomorphic adenoma</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Due to a blunt trauma, a young man in good general condition sustains a fracture of the right 10th rib and an apical pneumothorax of approximately 15%. There is no dyspnea, and the SpO2 on room air is within normal limits. The appropriate course of action is:</t>
+          <t>Due to a blunt trauma, a young man in good general condition sustains a fracture of the right 10th rib and an apical pneumothorax of approximately 15%. There is no dyspnea, and the SpO2 on room air is within normal limits. The appropriate course of action is</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>A 75-year-old man was found on ultrasound to have an abdominal aortic aneurysm measuring 6.0 centimeters in transverse diameter. Choose the correct option among the following:</t>
+          <t>A 75-year-old man was found on ultrasound to have an abdominal aortic aneurysm measuring 6.0 centimeters in transverse diameter. Choose the correct option among the following</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>A 26-year-old young man, with no significant prior medical history, arrives at the Emergency Department in ventricular fibrillation, and despite resuscitation maneuvers he dies. A postmortem diagnostic examination is performed, during which hypertrophy of the left ventricle and in particular of the interventricular septum is observed. Histological examination reveals disarray of the myocardial fibers. The observed picture is consistent with:</t>
+          <t>A 26-year-old young man, with no significant prior medical history, arrives at the Emergency Department in ventricular fibrillation, and despite resuscitation maneuvers he dies. A postmortem diagnostic examination is performed, during which hypertrophy of the left ventricle and in particular of the interventricular septum is observed. Histological examination reveals disarray of the myocardial fibers. The observed picture is consistent with</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>A 40-year-old female presents with a bilateral symmetrical whitish reticular lesion of the oral cavity; a biopsy of the lesion is performed, and histological examination reveals acanthosis, parakeratosis, and an intense band-like subepithelial lymphocytic infiltrate, with liquefaction of the basement membrane; the picture is consistent with:</t>
+          <t>A 40-year-old female presents with a bilateral symmetrical whitish reticular lesion of the oral cavity; a biopsy of the lesion is performed, and histological examination reveals acanthosis, parakeratosis, and an intense band-like subepithelial lymphocytic infiltrate, with liquefaction of the basement membrane; the picture is consistent with</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>A 67-year-old man is brought to the Emergency Department by his family in a confused state with a Glasgow Coma Scale of 11. An urgent CT scan is performed, revealing the findings shown in the image, which correspond to:</t>
+          <t>A 67-year-old man is brought to the Emergency Department by his family in a confused state with a Glasgow Coma Scale of 11. An urgent CT scan is performed, revealing the findings shown in the image, which correspond to</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>A 45-year-old woman with a history of substance abuse presents to the Emergency Department in a coma with respiratory depression; naloxone hydrochloride 0.4 mg is administered intravenously because it is:</t>
+          <t>A 45-year-old woman with a history of substance abuse presents to the Emergency Department in a coma with respiratory depression; naloxone hydrochloride 0.4 mg is administered intravenously because it is</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>A 23-year-old young man is brought to the Emergency Department in a coma with severe acute respiratory failure; the condition progresses to respiratory arrest. Several unsuccessful attempts at tracheal intubation are made, making it necessary to proceed with an emergency cricothyroidotomy. Cricothyroidotomy is indicated when:</t>
+          <t>A 23-year-old young man is brought to the Emergency Department in a coma with severe acute respiratory failure; the condition progresses to respiratory arrest. Several unsuccessful attempts at tracheal intubation are made, making it necessary to proceed with an emergency cricothyroidotomy. Cricothyroidotomy is indicated when</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>A 67-year-old woman is admitted for acute pulmonary embolism and anticoagulant therapy with intravenous sodium heparin is started. On the third day of hospitalization, she loses consciousness and presents with diffuse hypertonia in all four limbs and hemodynamic instability. The most probable and likely cause of the woman's current clinical condition is:</t>
+          <t>A 67-year-old woman is admitted for acute pulmonary embolism and anticoagulant therapy with intravenous sodium heparin is started. On the third day of hospitalization, she loses consciousness and presents with diffuse hypertonia in all four limbs and hemodynamic instability. The most probable and likely cause of the woman's current clinical condition is</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>A woman is bedridden due to a right femur fracture. During hospitalization, while awaiting surgery, she suddenly complains of a sensation of shortness of breath and chest pain. The on-call orthopedist is contacted, who calls the intensivist; the latter finds her agitated, dyspneic, and hypotensive. The intensivist immediately orders:</t>
+          <t>A woman is bedridden due to a right femur fracture. During hospitalization, while awaiting surgery, she suddenly complains of a sensation of shortness of breath and chest pain. The on-call orthopedist is contacted, who calls the intensivist; the latter finds her agitated, dyspneic, and hypotensive. The intensivist immediately orders</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>You are called to evaluate a 77-year-old man (history of ischemic heart disease, stable after revascularization 3 years earlier) who is to undergo knee arthroscopy under locoregional anesthesia. The anesthesiologist's assessment must necessarily include, among other things:</t>
+          <t>You are called to evaluate a 77-year-old man (history of ischemic heart disease, stable after revascularization 3 years earlier) who is to undergo knee arthroscopy under locoregional anesthesia. The anesthesiologist's assessment must necessarily include, among other things</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>A 27-year-old man is referred for genetic counseling by an assisted reproduction center. He underwent a semen analysis, which showed azoospermia, and a testicular ultrasound, which identified bilateral agenesis of the vas deferens. This finding is strongly suggestive of:</t>
+          <t>A 27-year-old man is referred for genetic counseling by an assisted reproduction center. He underwent a semen analysis, which showed azoospermia, and a testicular ultrasound, which identified bilateral agenesis of the vas deferens. This finding is strongly suggestive of</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Which of the following statements is correct:</t>
+          <t>Which of the following statements is correct</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Regarding Law 833/78 that established the National Health Service (SSN), indicate which of the following statements is FALSE:</t>
+          <t>Regarding Law 833/78 that established the National Health Service (SSN), indicate which of the following statements is FALSE</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Indicate which of the following statements about vaccine composition is true:</t>
+          <t>Indicate which of the following statements about vaccine composition is true</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Which of the following statements is correct regarding benzene:</t>
+          <t>Which of the following statements is correct regarding benzene</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2021_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2021_EN.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Gastroenterology</t>
+          <t>Gastroenterology; Infectious Diseases</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Dermatology and Venereology; General Surgery</t>
+          <t>Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Hematology; Oncology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Endocrinology; Pharmacology and Toxicology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Clinical Nutrition; Gastroenterology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Medical Genetics; Oncology</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Cardiology and Cardiac Surgery</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery</t>
+          <t>Pulmonology and Thoracic Surgery; Infectious Diseases</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Pediatrics</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>General Surgery; Gastroenterology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Hygiene, Epidemiology and Statistics</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Dermatology and Venereology; Gynecology and Obstetrics</t>
+          <t>Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Urology; Oncology</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Ophthalmology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Endocrinology</t>
+          <t>Otorhinolaryngology; General Surgery</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; General Surgery</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics; General Surgery</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Anesthesia and Intensive Care</t>
+          <t>Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Pulmonology and Thoracic Surgery</t>
+          <t>Pulmonology and Thoracic Surgery; Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Cardiology and Cardiac Surgery</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Oncology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Forensic Medicine; Hygiene, Epidemiology and Statistics</t>
+          <t>Hygiene, Epidemiology and Statistics; Forensic Medicine</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Occupational Medicine; Oncology</t>
+          <t>Occupational Medicine</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Occupational Medicine</t>
+          <t>Occupational Medicine; Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Forensic Medicine; Gynecology and Obstetrics</t>
+          <t>Forensic Medicine</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2021_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2021_EN.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/EN/xlsx/ITAMed_2021_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2021_EN.xlsx
@@ -7266,7 +7266,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Brain CT Scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_2021_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_2021_EN.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -473,15 +473,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Question Type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Image Category</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Image Path</t>
         </is>
@@ -544,6 +549,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -602,6 +612,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -662,10 +677,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Chest X-ray</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>images/2021/ssm202110228954.png</t>
         </is>
@@ -728,6 +748,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -786,6 +811,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -844,6 +874,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -902,6 +937,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -960,6 +1000,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1018,6 +1063,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1076,6 +1126,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1134,6 +1189,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1192,6 +1252,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1250,6 +1315,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1308,6 +1378,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1366,6 +1441,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1424,6 +1504,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1482,6 +1567,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1540,6 +1630,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1598,6 +1693,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1656,6 +1756,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1714,6 +1819,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1772,6 +1882,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1830,6 +1945,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1888,6 +2008,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1946,6 +2071,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2004,6 +2134,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2062,6 +2197,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2120,6 +2260,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2178,6 +2323,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2236,6 +2386,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2294,6 +2449,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2352,6 +2512,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2412,10 +2577,15 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>images/2021/ssm202110230454.png</t>
         </is>
@@ -2478,6 +2648,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2536,6 +2711,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2594,6 +2774,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2654,10 +2839,15 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>images/2021/ssm202110230654.png</t>
         </is>
@@ -2720,6 +2910,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2778,6 +2973,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2836,6 +3036,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2894,6 +3099,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2952,6 +3162,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3010,6 +3225,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3068,6 +3288,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3126,6 +3351,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3184,6 +3414,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3242,6 +3477,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3300,6 +3540,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3358,6 +3603,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3416,6 +3666,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3474,6 +3729,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3532,6 +3792,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3590,6 +3855,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3648,6 +3918,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3706,6 +3981,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3764,6 +4044,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3822,6 +4107,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3880,6 +4170,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3938,6 +4233,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3996,6 +4296,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4054,6 +4359,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4112,6 +4422,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4170,6 +4485,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4228,6 +4548,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4286,6 +4611,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4344,6 +4674,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4402,6 +4737,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4460,6 +4800,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4518,6 +4863,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4576,6 +4926,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4634,6 +4989,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4692,6 +5052,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4750,6 +5115,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4808,6 +5178,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4866,6 +5241,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4924,6 +5304,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4982,6 +5367,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5040,6 +5430,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5098,6 +5493,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5156,6 +5556,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5214,6 +5619,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5272,6 +5682,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5330,6 +5745,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5388,6 +5808,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5446,6 +5871,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5504,6 +5934,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5562,6 +5997,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5620,6 +6060,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5678,6 +6123,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5736,6 +6186,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5794,6 +6249,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5852,6 +6312,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5912,10 +6377,15 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
           <t>Fundus examination</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>images/2021/ssm202110233454.png</t>
         </is>
@@ -5978,6 +6448,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6036,6 +6511,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6094,6 +6574,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6152,6 +6637,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6210,6 +6700,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6268,6 +6763,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6326,6 +6826,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6384,6 +6889,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6442,6 +6952,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6500,6 +7015,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6558,6 +7078,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6616,6 +7141,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6674,6 +7204,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6732,6 +7267,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6790,6 +7330,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6848,6 +7393,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6906,6 +7456,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6964,6 +7519,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7022,6 +7582,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7080,6 +7645,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7138,6 +7708,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7198,10 +7773,15 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
           <t>Lower limb X-ray</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
+      <c r="O116" t="inlineStr">
         <is>
           <t>images/2021/ssm202110234554.png</t>
         </is>
@@ -7266,10 +7846,15 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr">
+      <c r="O117" t="inlineStr">
         <is>
           <t>images/2021/ssm202110234604.png</t>
         </is>
@@ -7332,6 +7917,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7390,6 +7980,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7448,6 +8043,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7506,6 +8106,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7564,6 +8169,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7622,6 +8232,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7680,6 +8295,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7738,6 +8358,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7796,6 +8421,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7854,6 +8484,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7912,6 +8547,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7970,6 +8610,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8028,6 +8673,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8086,6 +8736,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8144,6 +8799,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8202,6 +8862,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8260,6 +8925,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8318,6 +8988,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8376,6 +9051,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8434,6 +9114,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8492,6 +9177,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8550,6 +9240,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8608,6 +9303,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8664,6 +9364,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
